--- a/diseases/d053/2026-2029.xlsx
+++ b/diseases/d053/2026-2029.xlsx
@@ -7910,12 +7910,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -7940,12 +7940,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -7988,40 +7988,185 @@
       </c>
       <c r="AV51" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA51" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB51" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC51" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>D053</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>lassa</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Lassa</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>D053</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Lassa</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>拉沙热</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP52" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr"/>
+      <c r="AT52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV52" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW51" t="inlineStr">
+      <c r="AW52" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
+      <c r="AX52" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY51" t="inlineStr">
+      <c r="AY52" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
+      <c r="AZ52" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA51" t="inlineStr">
+      <c r="BA52" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB51" t="inlineStr">
+      <c r="BB52" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC51" t="inlineStr">
+      <c r="BC52" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -8143,7 +8288,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10">
@@ -8153,7 +8298,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d053/2026-2029.xlsx
+++ b/diseases/d053/2026-2029.xlsx
@@ -7185,12 +7185,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -7227,6 +7227,9 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
@@ -7263,42 +7266,42 @@
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7333,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -7360,7 +7363,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -7408,42 +7411,42 @@
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7508,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -7650,7 +7653,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -7795,7 +7798,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -7940,7 +7943,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -8055,12 +8058,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -8085,12 +8088,12 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N52" t="n">
@@ -8133,40 +8136,185 @@
       </c>
       <c r="AV52" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA52" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB52" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC52" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>D053</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>lassa</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Lassa</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>D053</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Lassa</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>拉沙热</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP53" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr"/>
+      <c r="AT53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV53" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW52" t="inlineStr">
+      <c r="AW53" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
+      <c r="AX53" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY52" t="inlineStr">
+      <c r="AY53" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
+      <c r="AZ53" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA52" t="inlineStr">
+      <c r="BA53" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB52" t="inlineStr">
+      <c r="BB53" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC52" t="inlineStr">
+      <c r="BC53" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -8288,7 +8436,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10">
@@ -8298,7 +8446,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d053/2026-2029.xlsx
+++ b/diseases/d053/2026-2029.xlsx
@@ -8320,6 +8320,151 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>D053</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>lassa</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Lassa</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>D053</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Lassa</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>拉沙热</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP54" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr"/>
+      <c r="AT54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV54" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA54" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB54" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC54" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8353,7 +8498,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8581,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10">
@@ -8446,7 +8591,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d053/2026-2029.xlsx
+++ b/diseases/d053/2026-2029.xlsx
@@ -8465,6 +8465,151 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>D053</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>lassa</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Lassa</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>D053</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Lassa</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>拉沙热</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP55" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr"/>
+      <c r="AT55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV55" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA55" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB55" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC55" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8498,7 +8643,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -8581,7 +8726,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10">
@@ -8591,7 +8736,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d053/2026-2029.xlsx
+++ b/diseases/d053/2026-2029.xlsx
@@ -5442,12 +5442,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5486,76 +5486,87 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_LASSA_FEVER</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS34" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_LASSA_FEVER</t>
+        </is>
+      </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -5582,17 +5593,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -5617,7 +5628,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -5631,76 +5642,165 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_LASSA_FEVER</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_LASSA_FEVER</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>拉沙热</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>country:CN-JS:national</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Official provincial report count for Lassa fever; source month is retained and absent rows remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN35" t="b">
+        <v>1</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS35" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_LASSA_FEVER</t>
+        </is>
+      </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -5732,12 +5832,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5762,7 +5862,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -5810,42 +5910,42 @@
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -5907,7 +6007,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -6052,7 +6152,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -6167,12 +6267,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -6197,21 +6297,18 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N39" t="n">
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
         <v>0</v>
       </c>
       <c r="R39" t="n">
@@ -6248,17 +6345,17 @@
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -6268,22 +6365,22 @@
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6315,12 +6412,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -6345,12 +6442,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -6393,42 +6490,42 @@
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC40" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6460,12 +6557,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -6490,7 +6587,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -6502,6 +6599,9 @@
         <v>0</v>
       </c>
       <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
         <v>0</v>
       </c>
       <c r="R41" t="n">
@@ -6538,17 +6638,17 @@
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -6558,22 +6658,22 @@
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC41" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -6605,12 +6705,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-FJ</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Fujian, China</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -6635,7 +6735,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -6649,76 +6749,87 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_LASSA_FEVER</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS42" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ42" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_LASSA_FEVER</t>
+        </is>
+      </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -6745,17 +6856,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-FJ</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Fujian, China</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -6780,7 +6891,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -6794,76 +6905,165 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_LASSA_FEVER</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_LASSA_FEVER</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>拉沙热</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>country:CN-FJ:national</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Official provincial report count for Lassa fever; source month is retained and absent rows remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN43" t="b">
+        <v>1</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS43" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ43" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_LASSA_FEVER</t>
+        </is>
+      </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
         </is>
       </c>
       <c r="BC43" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -6895,12 +7095,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -6925,7 +7125,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -6939,76 +7139,87 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_LASSA_FEVER</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS44" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ44" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_LASSA_FEVER</t>
+        </is>
+      </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -7035,17 +7246,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -7070,7 +7281,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -7084,76 +7295,165 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_LASSA_FEVER</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_LASSA_FEVER</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>拉沙热</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>country:CN-JS:national</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Official provincial report count for Lassa fever; source month is retained and absent rows remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN45" t="b">
+        <v>1</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS45" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_LASSA_FEVER</t>
+        </is>
+      </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -7185,12 +7485,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -7215,21 +7515,18 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N46" t="n">
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
@@ -7266,42 +7563,42 @@
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7630,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -7363,12 +7660,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -7411,42 +7708,42 @@
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -7508,12 +7805,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N48" t="n">
@@ -7653,12 +7950,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N49" t="n">
@@ -7798,12 +8095,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N50" t="n">
@@ -7943,12 +8240,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -8058,12 +8355,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -8088,7 +8385,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -8100,6 +8397,9 @@
         <v>0</v>
       </c>
       <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
         <v>0</v>
       </c>
       <c r="R52" t="n">
@@ -8136,17 +8436,17 @@
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -8156,22 +8456,22 @@
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -8203,12 +8503,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -8233,12 +8533,12 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N53" t="n">
@@ -8247,76 +8547,87 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_LASSA_FEVER</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS53" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ53" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_LASSA_FEVER</t>
+        </is>
+      </c>
       <c r="AT53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -8343,17 +8654,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -8378,12 +8689,12 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N54" t="n">
@@ -8392,76 +8703,165 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_LASSA_FEVER</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_LASSA_FEVER</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>拉沙热</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>country:CN-JS:national</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Official provincial report count for Lassa fever; source month is retained and absent rows remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN54" t="b">
+        <v>1</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS54" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ54" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_LASSA_FEVER</t>
+        </is>
+      </c>
       <c r="AT54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -8493,12 +8893,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -8523,12 +8923,12 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N55" t="n">
@@ -8571,40 +8971,1200 @@
       </c>
       <c r="AV55" t="inlineStr">
         <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA55" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB55" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC55" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>D053</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>lassa</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Lassa</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>D053</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Lassa</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>拉沙热</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP56" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr"/>
+      <c r="AT56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV56" t="inlineStr">
+        <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW55" t="inlineStr">
+      <c r="AW56" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
+      <c r="AX56" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY55" t="inlineStr">
+      <c r="AY56" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
+      <c r="AZ56" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA55" t="inlineStr">
+      <c r="BA56" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB55" t="inlineStr">
+      <c r="BB56" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC55" t="inlineStr">
+      <c r="BC56" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>D053</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>lassa</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Lassa</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>D053</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Lassa</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>拉沙热</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP57" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr"/>
+      <c r="AT57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV57" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA57" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB57" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC57" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>D053</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>lassa</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Lassa</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>D053</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Lassa</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>拉沙热</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP58" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr"/>
+      <c r="AT58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV58" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA58" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB58" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC58" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>D053</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>lassa</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Lassa</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>D053</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Lassa</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>拉沙热</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP59" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr"/>
+      <c r="AT59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV59" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA59" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB59" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC59" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>D053</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>lassa</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Lassa</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>D053</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Lassa</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>拉沙热</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP60" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr"/>
+      <c r="AT60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV60" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA60" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB60" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC60" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>D053</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>lassa</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Lassa</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>D053</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Lassa</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>拉沙热</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP61" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr"/>
+      <c r="AT61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV61" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA61" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB61" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC61" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>D053</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>lassa</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Lassa</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>D053</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Lassa</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>拉沙热</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP62" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr"/>
+      <c r="AT62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV62" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA62" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB62" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC62" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>D053</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>lassa</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Lassa</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>D053</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Lassa</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>拉沙热</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP63" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS63" t="inlineStr"/>
+      <c r="AT63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV63" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA63" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB63" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC63" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -8726,7 +10286,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10">
@@ -8736,7 +10296,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11">
@@ -8756,7 +10316,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -8766,7 +10326,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d053/2026-2029.xlsx
+++ b/diseases/d053/2026-2029.xlsx
@@ -10170,6 +10170,296 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>D053</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>lassa</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Lassa</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>D053</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Lassa</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>拉沙热</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP64" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr"/>
+      <c r="AT64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV64" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA64" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB64" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC64" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>D053</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>lassa</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Lassa</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>D053</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Lassa</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>拉沙热</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP65" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS65" t="inlineStr"/>
+      <c r="AT65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV65" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA65" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB65" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC65" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10203,7 +10493,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -10286,7 +10576,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
@@ -10296,7 +10586,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d053/2026-2029.xlsx
+++ b/diseases/d053/2026-2029.xlsx
@@ -10343,12 +10343,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N65" t="n">
@@ -10421,40 +10421,185 @@
       </c>
       <c r="AV65" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA65" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB65" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC65" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>D053</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>lassa</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Lassa</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>D053</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Lassa</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>拉沙热</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP66" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr"/>
+      <c r="AT66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV66" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW65" t="inlineStr">
+      <c r="AW66" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
+      <c r="AX66" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY65" t="inlineStr">
+      <c r="AY66" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
+      <c r="AZ66" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA65" t="inlineStr">
+      <c r="BA66" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB65" t="inlineStr">
+      <c r="BB66" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC65" t="inlineStr">
+      <c r="BC66" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -10576,7 +10721,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10">
@@ -10586,7 +10731,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d053/2026-2029.xlsx
+++ b/diseases/d053/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1661,6 +1671,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1806,6 +1821,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2546,6 +2566,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2691,6 +2716,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3431,6 +3461,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3576,6 +3611,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4316,6 +4356,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4461,6 +4506,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5349,6 +5399,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5884,6 +5939,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6612,6 +6672,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7537,6 +7602,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8410,6 +8480,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8945,6 +9020,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9815,6 +9895,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10538,6 +10623,11 @@
       <c r="S66" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">

--- a/diseases/d053/2026-2029.xlsx
+++ b/diseases/d053/2026-2029.xlsx
@@ -10695,6 +10695,151 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>D053</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>lassa</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Lassa</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>D053</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Lassa</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>拉沙热</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP67" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr"/>
+      <c r="AT67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV67" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA67" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB67" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC67" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10728,7 +10873,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -10811,7 +10956,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10">
@@ -10821,7 +10966,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11">
